--- a/outputs/019fbb91-20c2-7573-bd89-4731b032103d/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019fbb91-20c2-7573-bd89-4731b032103d/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R218cf9748d8b4aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R073888a90f714d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R5f820dbf49c74ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Raf6cce13e4144cd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R935bbfa5dcee4864"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Ra417ce902b7c4a92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Raddac6b3c69e4a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rd3ef4d61aa654bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf84ca10cd5ed4d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf5a2a1a12f2c4332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb2bd3d1075a745c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R8df505db60d1424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Reeff2b36bfb14845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R4f9e39ce2b484273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R686a524d7a334e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R602a90e65fc44325"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -11134,11 +11134,11 @@
       <x:c r="V144" s="62" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="W144" t="n">
+      <x:c r="W144" s="62" t="n">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="X144" t="str">
-        <x:v>PH50：前向SpotLight仅命中环境layer1并允许环境/怪物投影；玩家、穿戴物与手持枪固定在layer2，因此不会被自己的前向灯自投影。layer2只接受微弱无阴影正面补光；房间灯与太阳仍覆盖layer1+2，使玩家正常向地面投影。</x:v>
+        <x:v>PH50：前向SpotLight仅命中环境layer1并保留环境/怪物投影；玩家、穿戴物与手持枪统一位于layer2且cast_shadow=OFF，不进入随身灯shadow map。layer2只接受无阴影正面补光；已通过真实渲染与自投影专项验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -12046,11 +12046,11 @@
       <x:c r="V156" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W156" s="70" t="str">
-        <x:v>用户提供 Blender 源文件 / Codex 模块化拆分</x:v>
+      <x:c r="W156" s="71" t="n">
+        <x:v>46235</x:v>
       </x:c>
       <x:c r="X156" s="70" t="str">
-        <x:v>PH43：继续复用v006 1.5m模型与稳定AssetID；Player3D玩法碰撞升级为高1.5m、半径0.34m的VirtualCollisionCapsule。顶层状态扩展为idle/moving/dashing/hurt/locked/falling/landing/dead；下落收腿、耳后扬与落地压缩/回弹均由既有刚性节点程序驱动，不新增GLB或贴图。</x:v>
+        <x:v>PH50：bunny01主体、耳朵、手脚、DIY穿戴物与WeaponSocket下手持武器统一使用render layer2、GI关闭、cast_shadow=OFF；角色仍接收专用无阴影柔光，但不会在玩家随身灯前方产生放大自投影。</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="118" customHeight="1">
@@ -12576,11 +12576,11 @@
       <x:c r="V163" s="71" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="W163" s="70" t="n">
+      <x:c r="W163" s="71" t="n">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="X163" s="70" t="str">
-        <x:v>PH50：基地墙体与楼顶/战斗房统一为5m实墙、5m门墙和独立L拐角Mesh组件，删除整条Box拉伸墙路径。98—96层普通房固定30×25m（6×5格），按5m走廊间距重排为紧凑环线；95层保留90×90m Boss区并同步压缩前置房。全层通过无重叠、双向门、实际通行、楼梯钥匙门、随机种子与撤离回归。</x:v>
+        <x:v>PH50：250m整层与65m核心不变；99层30×30m基地、98—96层30×25m/6×5房间和95层Boss区均以5m格线边界生成。门墙组件、RoomDoor3D与走廊端点按两端真实门槽求交；楼梯只在上层楼板开15×30m模块洞，落地层保持完整覆盖。</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="132" customHeight="1">
@@ -13056,7 +13056,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra77edd0bfb8843dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18073fb8f3f14812"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17619,26 +17619,49 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="str">
+    <x:row r="34" ht="96" customHeight="1">
+      <x:c r="A34" s="63" t="str">
         <x:v>v1.28</x:v>
       </x:c>
-      <x:c r="B34" t="str">
+      <x:c r="B34" s="63" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
-      <x:c r="C34" t="str">
+      <x:c r="C34" s="63" t="str">
         <x:v>PH50三十乘二十五房间、模块化基地墙与分层投影修复</x:v>
       </x:c>
-      <x:c r="D34" t="str">
+      <x:c r="D34" s="63" t="str">
         <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-WALL-SOLID-5M; ENV-TOWER-WALL-DOOR-5M; PRP-WASTELAND-LIGHT-3D; VFX-PLAYER-FLASHLIGHT-3D; ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="E34" t="str">
+      <x:c r="E34" s="63" t="str">
         <x:v>98—96层普通房统一30×25m/6×5格并紧凑重排；基地删除整墙拉伸路径，改用独立5m墙、门墙和L拐角组件；墙段A/B材质交替；房间灯递归流送并让玩家/怪物投影；前向灯只照环境层，不对玩家自投影；普通行动区恢复初始1钥匙与唯一STANDARD信标。</x:v>
       </x:c>
-      <x:c r="F34" t="str">
+      <x:c r="F34" s="63" t="str">
         <x:v>不新增AssetID、GLB或贴图；复用既有5m模块与两套墙材质。塔楼、94门物理通行、3D核心、四主题完整流程、房灯、视野输入、背包武器、换弹、撤离、运行安全和性能预算全部通过，并完成真实渲染复核。</x:v>
       </x:c>
-      <x:c r="G34" t="str">
+      <x:c r="G34" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="108" customHeight="1">
+      <x:c r="A35" s="63" t="str">
+        <x:v>v1.29</x:v>
+      </x:c>
+      <x:c r="B35" s="64" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C35" s="63" t="str">
+        <x:v>PH50 五米组件坐标与玩家灯光自投影修复</x:v>
+      </x:c>
+      <x:c r="D35" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D / ENV-TOWER-FLOOR-TILE-5M / ENV-TOWER-WALL-SOLID-5M / ENV-TOWER-STAIRWELL-GENERIC-9M / CHR-PLY-CAPSULE01-BUNNY01 / WPN-GUN-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E35" s="63" t="str">
+        <x:v>基底层改为合法6×6组件边界；98—95层30×25房间按5m格线重排；门墙、交互门与走廊端点由两端真实门槽求交；楼梯只挖上层楼板；玩家/配件/手持武器禁投影，前向灯仍保留环境与怪物阴影。</x:v>
+      </x:c>
+      <x:c r="F35" s="63" t="str">
+        <x:v>AssetID与GLB不变；Godot关卡坐标、楼板覆盖和渲染属性更新；TOWER_GRID_COMPONENT_ALIGNMENT_OK、TOWER_DESCENT_FLOW_OK、94门通行、灯光/性能/视觉回归通过。</x:v>
+      </x:c>
+      <x:c r="G35" s="63" t="str">
         <x:v>Codex</x:v>
       </x:c>
     </x:row>

--- a/outputs/019fbb91-20c2-7573-bd89-4731b032103d/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019fbb91-20c2-7573-bd89-4731b032103d/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf84ca10cd5ed4d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf5a2a1a12f2c4332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rb2bd3d1075a745c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R8df505db60d1424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Reeff2b36bfb14845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R4f9e39ce2b484273"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R686a524d7a334e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R602a90e65fc44325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcaaab8bdaaa2428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rc281819524a44e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Rd6466099b9344e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Rca9e7a8f8f724486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rbe08f792abae40ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rd228f9c63d8147d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R21176932c385478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R5f70b6e6332a46e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8788,13 +8788,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V113" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W113" s="70" t="str">
         <x:v>原创程序几何</x:v>
       </x:c>
       <x:c r="X113" s="70" t="str">
-        <x:v>PH49：原先项目外shellstorm2-art/blender中的三份角色Blender源已按稳定命名归档到assets/art/characters/player/chr_player_capsule01_3d/source/，SHA-256与原件一致；运行时场景路径不变，后续不再依赖仓库外资产。</x:v>
+        <x:v>玩家随身三灯通过 layer 1/2 隔离避免自身投影；角色网格恢复外部太阳光/室内灯投影，GI保持关闭；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -12648,13 +12648,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V164" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W164" s="70" t="str">
         <x:v>程序生成Blender源集合</x:v>
       </x:c>
       <x:c r="X164" s="70" t="str">
-        <x:v>PH44：整层由67×67调整为50×50个5m模块，物理尺寸250×250m、满铺2500块；地板仍由模块化MultiMesh渲染并保留独立StaticBody承重。四向楼梯洞口改用对齐5m世界矩形换算网格，避免尺寸与位移单位错位。</x:v>
+        <x:v>塔楼地砖统一低金属0.08/高粗糙0.90，降低太阳与室内灯高光；A/B双色交替保留；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="132" customHeight="1">
@@ -12722,13 +12722,13 @@
         <x:v>Codex</x:v>
       </x:c>
       <x:c r="V165" s="71" t="n">
-        <x:v>46233</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="W165" s="70" t="n">
         <x:v>46235</x:v>
       </x:c>
       <x:c r="X165" s="70" t="str">
-        <x:v>PH50：99层基地和30×25m战斗房的每个5m墙位均实例化为独立MeshInstance3D；相邻墙段按绝对段号交替使用A/B两套材质，门墙和四个L拐角沿用同一交替规则。门洞两侧碰撞按5m网格合并，外层250m楼体仍保留MultiMesh批渲染以满足性能预算。</x:v>
+        <x:v>实墙、门墙、L拐角统一0—9m高度；仅南面朝北墙标记摄像机交互；隐藏连接器不保留阻挡碰撞；verify_tower_lighting_wall_combat_regressions.tscn</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="132" customHeight="1">
@@ -13056,7 +13056,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18073fb8f3f14812"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3993304e8f974db9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17665,6 +17665,29 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="72" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>v1.30</x:v>
+      </x:c>
+      <x:c r="B36" s="62" t="n">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C36" s="63" t="str">
+        <x:v>PH51 灯光投影、地砖反光、9m南墙与刷怪软锁修复</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D / ENV-TOWER-FLOOR-TILE-5M / ENV-TOWER-WALL-SOLID-5M / Dungeon3D</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>角色恢复太阳/室内灯投影但三盏随身灯不自投影；地砖降反光；实墙/门墙/拐角统一9m并仅南墙参与摄像机交互；隐藏连接器碰撞随显隐；敌对房间增加生成兜底与旧状态修复。</x:v>
+      </x:c>
+      <x:c r="F36" s="63" t="str">
+        <x:v>不新增AssetID；仅修正既有组件配置与生成/碰撞逻辑；全量回归PASS</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>
